--- a/Excel Assignment 1 - Data Exploration.xls (23-05-26).xlsx
+++ b/Excel Assignment 1 - Data Exploration.xls (23-05-26).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" activeTab="1"/>
+    <workbookView windowWidth="20490" windowHeight="7500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Dataset" sheetId="1" r:id="rId1"/>
@@ -810,12 +810,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -940,7 +955,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -952,34 +967,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1064,7 +1079,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1072,28 +1087,31 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1112,6 +1130,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1599,739 +1620,739 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="5"/>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="19">
         <v>1000</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="19">
         <v>30</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="17"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D3" s="20">
         <v>80</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="20">
         <v>15</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="17"/>
+      <c r="G3" s="19"/>
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="19">
         <v>130</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="19">
         <v>40</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="17"/>
+      <c r="G4" s="19"/>
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <v>900</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="20">
         <v>25</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="17"/>
+      <c r="G5" s="19"/>
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="19">
         <v>70</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="19">
         <v>20</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="17"/>
+      <c r="G6" s="19"/>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="20">
         <v>200</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="20">
         <v>45</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="17"/>
+      <c r="G7" s="19"/>
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="19">
         <v>30</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="19">
         <v>5</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="17"/>
+      <c r="G8" s="19"/>
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="20">
         <v>90</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="20">
         <v>35</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="17"/>
+      <c r="G9" s="19"/>
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="19">
         <v>500</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="19">
         <v>50</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="17"/>
+      <c r="G10" s="19"/>
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="20">
         <v>130</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="20">
         <v>10</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="17"/>
+      <c r="G11" s="19"/>
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="19">
         <v>950</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="19">
         <v>25</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="17"/>
+      <c r="G12" s="19"/>
     </row>
     <row r="13" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="20">
         <v>90</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="20">
         <v>40</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="17"/>
+      <c r="G13" s="19"/>
     </row>
     <row r="14" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="19">
         <v>120</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="19">
         <v>35</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="17"/>
+      <c r="G14" s="19"/>
     </row>
     <row r="15" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="20">
         <v>150</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="20">
         <v>15</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="G15" s="17"/>
+      <c r="G15" s="19"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="19">
         <v>250</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="19">
         <v>20</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="G16" s="17"/>
+      <c r="G16" s="19"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="20">
         <v>50</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="20">
         <v>35</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="F17" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G17" s="17"/>
+      <c r="G17" s="19"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="19">
         <v>160</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="19">
         <v>15</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="G18" s="17"/>
+      <c r="G18" s="19"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="20">
         <v>980</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="20">
         <v>10</v>
       </c>
-      <c r="F19" s="18" t="s">
+      <c r="F19" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="G19" s="17"/>
+      <c r="G19" s="19"/>
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="19">
         <v>150</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="19">
         <v>15</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="17"/>
+      <c r="G20" s="19"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="20">
         <v>200</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="20">
         <v>10</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="G21" s="17"/>
+      <c r="G21" s="19"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="19">
         <v>700</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="19">
         <v>50</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="17"/>
+      <c r="G22" s="19"/>
     </row>
     <row r="23" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="18">
+      <c r="D23" s="20">
         <v>80</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="20">
         <v>20</v>
       </c>
-      <c r="F23" s="18" t="s">
+      <c r="F23" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="17"/>
+      <c r="G23" s="19"/>
     </row>
     <row r="24" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="19">
         <v>150</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="19">
         <v>30</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="G24" s="17"/>
+      <c r="G24" s="19"/>
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="18">
+      <c r="D25" s="20">
         <v>50</v>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="20">
         <v>35</v>
       </c>
-      <c r="F25" s="18" t="s">
+      <c r="F25" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G25" s="19"/>
+      <c r="G25" s="21"/>
     </row>
     <row r="26" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="19">
         <v>800</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="19">
         <v>45</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="F26" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="G26" s="17"/>
+      <c r="G26" s="19"/>
     </row>
     <row r="27" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="D27" s="18">
+      <c r="D27" s="20">
         <v>130</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="20">
         <v>25</v>
       </c>
-      <c r="F27" s="18" t="s">
+      <c r="F27" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="G27" s="17"/>
+      <c r="G27" s="19"/>
     </row>
     <row r="28" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="19">
         <v>400</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="19">
         <v>40</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="G28" s="17"/>
+      <c r="G28" s="19"/>
     </row>
     <row r="29" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="18">
+      <c r="D29" s="20">
         <v>230</v>
       </c>
-      <c r="E29" s="18">
+      <c r="E29" s="20">
         <v>20</v>
       </c>
-      <c r="F29" s="18" t="s">
+      <c r="F29" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="G29" s="19"/>
+      <c r="G29" s="21"/>
     </row>
     <row r="30" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="19">
         <v>60</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="19">
         <v>30</v>
       </c>
-      <c r="F30" s="17" t="s">
+      <c r="F30" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G30" s="17"/>
+      <c r="G30" s="19"/>
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="D31" s="18">
+      <c r="D31" s="20">
         <v>40</v>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="20">
         <v>10</v>
       </c>
-      <c r="F31" s="18" t="s">
+      <c r="F31" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G31" s="17"/>
+      <c r="G31" s="19"/>
     </row>
     <row r="32" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="19">
         <v>130</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="19">
         <v>5</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="F32" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="G32" s="17"/>
+      <c r="G32" s="19"/>
     </row>
     <row r="33" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="D33" s="18">
+      <c r="D33" s="20">
         <v>50</v>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="20">
         <v>50</v>
       </c>
-      <c r="F33" s="18" t="s">
+      <c r="F33" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="G33" s="17"/>
+      <c r="G33" s="19"/>
     </row>
     <row r="34" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A34" s="17" t="s">
+      <c r="A34" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D34" s="17">
+      <c r="D34" s="19">
         <v>950</v>
       </c>
-      <c r="E34" s="17">
+      <c r="E34" s="19">
         <v>25</v>
       </c>
-      <c r="F34" s="17" t="s">
+      <c r="F34" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="G34" s="17"/>
+      <c r="G34" s="19"/>
     </row>
     <row r="35" ht="15.75" customHeight="1" spans="1:7">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="18">
+      <c r="D35" s="20">
         <v>100</v>
       </c>
-      <c r="E35" s="18">
+      <c r="E35" s="20">
         <v>20</v>
       </c>
-      <c r="F35" s="18" t="s">
+      <c r="F35" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G35" s="17"/>
+      <c r="G35" s="19"/>
     </row>
     <row r="36" ht="15.75" customHeight="1"/>
     <row r="37" ht="15.75" customHeight="1"/>
@@ -3350,7 +3371,7 @@
       <c r="J1" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="K1" s="3"/>
+      <c r="K1" s="5"/>
       <c r="L1" s="5"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:14">
@@ -3388,29 +3409,29 @@
         <f>MID(A2,4,3)</f>
         <v>JAN</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="8" t="s">
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="9" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:14">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="11">
         <v>80</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="10">
         <v>15</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G3" s="6" t="str">
@@ -3429,8 +3450,8 @@
         <f>MID(A3,4,3)</f>
         <v>FEB</v>
       </c>
-      <c r="K3" s="9"/>
-      <c r="L3" s="6"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:14">
       <c r="A4" s="6" t="s">
@@ -3467,29 +3488,29 @@
         <f t="shared" ref="J3:J35" si="3">MID(A4,4,3)</f>
         <v>MAR</v>
       </c>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="11" t="s">
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="12" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:14">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="11">
         <v>900</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="10">
         <v>25</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="10" t="s">
         <v>9</v>
       </c>
       <c r="G5" s="6" t="str">
@@ -3508,8 +3529,8 @@
         <f t="shared" si="3"/>
         <v>APR</v>
       </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="6"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:14">
       <c r="A6" s="6" t="s">
@@ -3546,29 +3567,29 @@
         <f t="shared" si="3"/>
         <v>MAY</v>
       </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="12" t="s">
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="13" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:14">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="11">
         <v>200</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="10">
         <v>45</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="10" t="s">
         <v>9</v>
       </c>
       <c r="G7" s="6" t="str">
@@ -3587,9 +3608,9 @@
         <f t="shared" si="3"/>
         <v>JUN</v>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="13">
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="14">
         <v>10100</v>
       </c>
     </row>
@@ -3628,26 +3649,26 @@
         <f t="shared" si="3"/>
         <v>JUL</v>
       </c>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:14">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="11">
         <v>90</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="10">
         <v>35</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G9" s="6" t="str">
@@ -3666,9 +3687,9 @@
         <f t="shared" si="3"/>
         <v>AUG</v>
       </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="11" t="s">
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="12" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3707,29 +3728,29 @@
         <f t="shared" si="3"/>
         <v>SEP</v>
       </c>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="12" t="s">
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="13" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:14">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="11">
         <v>130</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="10">
         <v>10</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="10" t="s">
         <v>24</v>
       </c>
       <c r="G11" s="6" t="str">
@@ -3748,9 +3769,9 @@
         <f t="shared" si="3"/>
         <v>OCT</v>
       </c>
-      <c r="K11" s="9"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="13">
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="14">
         <v>34</v>
       </c>
     </row>
@@ -3789,26 +3810,26 @@
         <f t="shared" si="3"/>
         <v>JUN</v>
       </c>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:14">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="11">
         <v>90</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="10">
         <v>40</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G13" s="6" t="str">
@@ -3827,9 +3848,9 @@
         <f t="shared" si="3"/>
         <v>NOV</v>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="12"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="13"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:14">
       <c r="A14" s="6" t="s">
@@ -3866,9 +3887,9 @@
         <f t="shared" si="3"/>
         <v>DEC</v>
       </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="11" t="s">
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="12" t="s">
         <v>102</v>
       </c>
       <c r="N14" s="1" t="s">
@@ -3876,22 +3897,22 @@
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:14">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="11">
         <v>150</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="10">
         <v>15</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="10" t="s">
         <v>9</v>
       </c>
       <c r="G15" s="6" t="str">
@@ -3910,9 +3931,9 @@
         <f t="shared" si="3"/>
         <v>FEB</v>
       </c>
-      <c r="K15" s="9"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="14"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="15"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:14">
       <c r="A16" s="6" t="s">
@@ -3949,29 +3970,29 @@
         <f t="shared" si="3"/>
         <v>APR</v>
       </c>
-      <c r="K16" s="6"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="15" t="s">
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="16" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="11">
         <v>50</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="10">
         <v>35</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="10" t="s">
         <v>53</v>
       </c>
       <c r="G17" s="6" t="str">
@@ -3990,9 +4011,9 @@
         <f t="shared" si="3"/>
         <v>AUG</v>
       </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="13">
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="14">
         <v>297.058823529412</v>
       </c>
     </row>
@@ -4031,27 +4052,27 @@
         <f t="shared" si="3"/>
         <v>AUG</v>
       </c>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="14"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="15"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="11">
         <v>980</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="10">
         <v>10</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="10" t="s">
         <v>9</v>
       </c>
       <c r="G19" s="6" t="str">
@@ -4070,8 +4091,8 @@
         <f t="shared" si="3"/>
         <v>JAN</v>
       </c>
-      <c r="K19" s="9"/>
-      <c r="L19" s="6"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
       <c r="A20" s="6" t="s">
@@ -4108,26 +4129,26 @@
         <f t="shared" si="3"/>
         <v>MAR</v>
       </c>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="11">
         <v>200</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="10">
         <v>10</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="10" t="s">
         <v>24</v>
       </c>
       <c r="G21" s="6" t="str">
@@ -4146,9 +4167,9 @@
         <f t="shared" si="3"/>
         <v>AUG</v>
       </c>
-      <c r="K21" s="9"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="8" t="s">
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="9" t="s">
         <v>105</v>
       </c>
     </row>
@@ -4187,26 +4208,26 @@
         <f t="shared" si="3"/>
         <v>MAY</v>
       </c>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="11">
         <v>80</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="10">
         <v>20</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G23" s="6" t="str">
@@ -4225,9 +4246,9 @@
         <f t="shared" si="3"/>
         <v>JAN</v>
       </c>
-      <c r="K23" s="9"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="11" t="s">
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="12" t="s">
         <v>106</v>
       </c>
     </row>
@@ -4266,26 +4287,26 @@
         <f t="shared" si="3"/>
         <v>JUL</v>
       </c>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="11">
         <v>50</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="10">
         <v>35</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="10" t="s">
         <v>53</v>
       </c>
       <c r="G25" s="6" t="str">
@@ -4304,9 +4325,9 @@
         <f t="shared" si="3"/>
         <v>AUG</v>
       </c>
-      <c r="K25" s="9"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="12" t="s">
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="13" t="s">
         <v>107</v>
       </c>
     </row>
@@ -4345,29 +4366,29 @@
         <f t="shared" si="3"/>
         <v>SEP</v>
       </c>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="13">
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="14">
         <v>30</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="11">
         <v>130</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="10">
         <v>25</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G27" s="6" t="str">
@@ -4386,8 +4407,8 @@
         <f t="shared" si="3"/>
         <v>JUN</v>
       </c>
-      <c r="K27" s="9"/>
-      <c r="L27" s="6"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
       <c r="A28" s="6" t="s">
@@ -4424,29 +4445,29 @@
         <f t="shared" si="3"/>
         <v>JUL</v>
       </c>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="12" t="s">
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="13" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="11">
         <v>230</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="10">
         <v>20</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="10" t="s">
         <v>9</v>
       </c>
       <c r="G29" s="6" t="str">
@@ -4465,9 +4486,9 @@
         <f t="shared" si="3"/>
         <v>APR</v>
       </c>
-      <c r="K29" s="9"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="13">
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="M29" s="14">
         <v>1000</v>
       </c>
     </row>
@@ -4506,26 +4527,26 @@
         <f t="shared" si="3"/>
         <v>MAR</v>
       </c>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
     </row>
     <row r="31" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="11">
         <v>40</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="10">
         <v>10</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="10" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="6" t="str">
@@ -4544,8 +4565,8 @@
         <f t="shared" si="3"/>
         <v>APR</v>
       </c>
-      <c r="K31" s="9"/>
-      <c r="L31" s="6"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
       <c r="A32" s="6" t="s">
@@ -4582,26 +4603,26 @@
         <f t="shared" si="3"/>
         <v>MAY</v>
       </c>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="11">
         <v>50</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="10">
         <v>50</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G33" s="6" t="str">
@@ -4620,9 +4641,9 @@
         <f t="shared" si="3"/>
         <v>DEC</v>
       </c>
-      <c r="K33" s="9"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="8" t="s">
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="9" t="s">
         <v>109</v>
       </c>
     </row>
@@ -4661,26 +4682,26 @@
         <f t="shared" si="3"/>
         <v>JUN</v>
       </c>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="11">
         <v>100</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="10">
         <v>20</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="10" t="s">
         <v>53</v>
       </c>
       <c r="G35" s="6" t="str">
@@ -4699,15 +4720,15 @@
         <f t="shared" si="3"/>
         <v>JUL</v>
       </c>
-      <c r="K35" s="9"/>
-      <c r="L35" s="6"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
       <c r="M35" s="1" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
       <c r="D36" s="2"/>
-      <c r="M36" s="13">
+      <c r="M36" s="14">
         <v>970</v>
       </c>
     </row>
@@ -4719,7 +4740,7 @@
     </row>
     <row r="39" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
       <c r="D39" s="2"/>
-      <c r="M39" s="8" t="s">
+      <c r="M39" s="9" t="s">
         <v>111</v>
       </c>
     </row>
@@ -4728,7 +4749,7 @@
     </row>
     <row r="41" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
       <c r="D41" s="2"/>
-      <c r="M41" s="12" t="s">
+      <c r="M41" s="13" t="s">
         <v>112</v>
       </c>
     </row>
@@ -4737,7 +4758,7 @@
     </row>
     <row r="43" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
       <c r="D43" s="2"/>
-      <c r="M43" s="13">
+      <c r="M43" s="14">
         <v>8050</v>
       </c>
     </row>
@@ -4749,7 +4770,7 @@
     </row>
     <row r="46" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
       <c r="D46" s="2"/>
-      <c r="M46" s="11" t="s">
+      <c r="M46" s="12" t="s">
         <v>113</v>
       </c>
     </row>
@@ -4758,7 +4779,7 @@
     </row>
     <row r="48" s="1" customFormat="1" ht="15.75" customHeight="1" spans="1:13">
       <c r="D48" s="2"/>
-      <c r="M48" s="12" t="s">
+      <c r="M48" s="13" t="s">
         <v>114</v>
       </c>
     </row>
@@ -4767,7 +4788,7 @@
     </row>
     <row r="50" s="1" customFormat="1" ht="15.75" customHeight="1" spans="4:13">
       <c r="D50" s="2"/>
-      <c r="M50" s="13">
+      <c r="M50" s="14">
         <v>11</v>
       </c>
     </row>
@@ -4779,7 +4800,7 @@
     </row>
     <row r="53" s="1" customFormat="1" ht="15.75" customHeight="1" spans="4:13">
       <c r="D53" s="2"/>
-      <c r="M53" s="8" t="s">
+      <c r="M53" s="9" t="s">
         <v>115</v>
       </c>
     </row>
